--- a/results/20260514_v2/evaluation_VirusPseAAC_noisy_0.3_ecc.xlsx
+++ b/results/20260514_v2/evaluation_VirusPseAAC_noisy_0.3_ecc.xlsx
@@ -981,12 +981,8 @@
           <t>auc_macro</t>
         </is>
       </c>
-      <c r="H20" t="n">
-        <v>0.67754</v>
-      </c>
-      <c r="I20" t="n">
-        <v>0.06895</v>
-      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
